--- a/data/WHRS LOG - CC IGUACU(ROI included) - SAMPLE LOG.xlsx
+++ b/data/WHRS LOG - CC IGUACU(ROI included) - SAMPLE LOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VENKAT\Downloads\WHRS_EPS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VENKAT\Downloads\LEARNING\WHRS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9E88DC-FAEE-46E9-BBEF-274472BD670D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA88192-6BF3-4E5A-9DD2-C1BB79CBF60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4576,13 +4576,19 @@
       <c r="T34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W34" s="1" t="str">
+      <c r="U34" s="1">
+        <v>45368</v>
+      </c>
+      <c r="V34" s="1">
+        <v>47571</v>
+      </c>
+      <c r="W34" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X34" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V33</f>
-        <v>-47571</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="6" t="b">
         <f>IF(AND(Table1[[#This Row],[WHRS KW RECOVERED PER DAY]]&lt;&gt;0,Table1[[#This Row],[WHRS RH]]&lt;&gt;0),ROUND(Table1[[#This Row],[WHRS KW RECOVERED PER DAY]]/Table1[[#This Row],[WHRS RH]],1))</f>
@@ -4604,13 +4610,13 @@
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="AH34" s="1" t="str">
+      <c r="AH34" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AI34" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="1">
         <f>IF(AH34="", "", SUM($AH$4:AH34))</f>
-        <v/>
+        <v>10478.92886</v>
       </c>
       <c r="AJ34" s="9"/>
     </row>
@@ -4639,9 +4645,15 @@
       <c r="T35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W35" s="1" t="str">
+      <c r="U35" s="1">
+        <v>45368</v>
+      </c>
+      <c r="V35" s="1">
+        <v>47571</v>
+      </c>
+      <c r="W35" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U34)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X35" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V34</f>
@@ -4667,13 +4679,13 @@
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="AH35" s="1" t="str">
+      <c r="AH35" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AI35" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="1">
         <f>IF(AH35="", "", SUM($AH$4:AH35))</f>
-        <v/>
+        <v>10478.92886</v>
       </c>
       <c r="AJ35" s="9"/>
     </row>
@@ -4702,9 +4714,15 @@
       <c r="T36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W36" s="1" t="str">
+      <c r="U36" s="1">
+        <v>45368</v>
+      </c>
+      <c r="V36" s="1">
+        <v>47571</v>
+      </c>
+      <c r="W36" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X36" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V35</f>
@@ -4730,13 +4748,13 @@
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="AH36" s="1" t="str">
+      <c r="AH36" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AI36" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="1">
         <f>IF(AH36="", "", SUM($AH$4:AH36))</f>
-        <v/>
+        <v>10478.92886</v>
       </c>
       <c r="AJ36" s="9"/>
     </row>
@@ -4765,9 +4783,15 @@
       <c r="T37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W37" s="1" t="str">
+      <c r="U37" s="1">
+        <v>45368</v>
+      </c>
+      <c r="V37" s="1">
+        <v>47571</v>
+      </c>
+      <c r="W37" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U36)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X37" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V36</f>
@@ -4793,13 +4817,13 @@
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="AH37" s="1" t="str">
+      <c r="AH37" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AI37" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="1">
         <f>IF(AH37="", "", SUM($AH$4:AH37))</f>
-        <v/>
+        <v>10478.92886</v>
       </c>
       <c r="AJ37" s="9"/>
     </row>
@@ -4828,9 +4852,15 @@
       <c r="T38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W38" s="1" t="str">
+      <c r="U38" s="1">
+        <v>45368</v>
+      </c>
+      <c r="V38" s="1">
+        <v>47571</v>
+      </c>
+      <c r="W38" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U37)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="X38" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V37</f>
@@ -4856,13 +4886,13 @@
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="AH38" s="1" t="str">
+      <c r="AH38" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AI38" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="1">
         <f>IF(AH38="", "", SUM($AH$4:AH38))</f>
-        <v/>
+        <v>10478.92886</v>
       </c>
       <c r="AJ38" s="9"/>
     </row>
@@ -4935,15 +4965,15 @@
       </c>
       <c r="W39" s="1">
         <f>IF(Table1[[#This Row],[WHRS NET KW TOTAL]]="","", Table1[[#This Row],[WHRS NET KW TOTAL]]-U38)</f>
-        <v>48478</v>
+        <v>3110</v>
       </c>
       <c r="X39" s="6">
         <f>Table1[[#This Row],[WHRS  KW TOTAL]]-V38</f>
-        <v>50821</v>
+        <v>3250</v>
       </c>
       <c r="Y39" s="6">
         <f>IF(AND(Table1[[#This Row],[WHRS KW RECOVERED PER DAY]]&lt;&gt;0,Table1[[#This Row],[WHRS RH]]&lt;&gt;0),ROUND(Table1[[#This Row],[WHRS KW RECOVERED PER DAY]]/Table1[[#This Row],[WHRS RH]],1))</f>
-        <v>4235.1000000000004</v>
+        <v>270.8</v>
       </c>
       <c r="Z39" s="8">
         <v>12</v>
@@ -4973,11 +5003,11 @@
       </c>
       <c r="AH39" s="1">
         <f t="shared" si="3"/>
-        <v>7250.7575040000011</v>
+        <v>465.1564800000001</v>
       </c>
       <c r="AI39" s="1">
         <f>IF(AH39="", "", SUM($AH$4:AH39))</f>
-        <v>17729.686364000001</v>
+        <v>10944.08534</v>
       </c>
       <c r="AJ39" s="9"/>
     </row>
@@ -5092,7 +5122,7 @@
       </c>
       <c r="AI40" s="1">
         <f>IF(AH40="", "", SUM($AH$4:AH40))</f>
-        <v>18229.841756000002</v>
+        <v>11444.240732</v>
       </c>
       <c r="AJ40" s="9"/>
     </row>
@@ -5207,7 +5237,7 @@
       </c>
       <c r="AI41" s="1">
         <f>IF(AH41="", "", SUM($AH$4:AH41))</f>
-        <v>18765.444764</v>
+        <v>11979.84374</v>
       </c>
       <c r="AJ41" s="9"/>
     </row>
@@ -5322,7 +5352,7 @@
       </c>
       <c r="AI42" s="1">
         <f>IF(AH42="", "", SUM($AH$4:AH42))</f>
-        <v>19232.695196000001</v>
+        <v>12447.094172000001</v>
       </c>
       <c r="AJ42" s="9"/>
     </row>
@@ -5437,7 +5467,7 @@
       </c>
       <c r="AI43" s="1">
         <f>IF(AH43="", "", SUM($AH$4:AH43))</f>
-        <v>19585.825244</v>
+        <v>12800.224220000002</v>
       </c>
       <c r="AJ43" s="9"/>
     </row>
@@ -38451,6 +38481,9 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="X39" calculatedColumn="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
